--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486515_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486515_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.791</v>
+        <v>3.0589</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4591</v>
+        <v>3.5593</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3318</v>
+        <v>-0.5004</v>
       </c>
       <c r="G2" t="n">
         <v>1.0847</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>6.2924</v>
+        <v>3.5603</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5545</v>
+        <v>2.6546</v>
       </c>
       <c r="U2" t="n">
-        <v>1.738</v>
+        <v>0.9058</v>
       </c>
       <c r="V2" t="n">
         <v>-3.5438</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4916</v>
+        <v>2.4714</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8475</v>
+        <v>0.5808</v>
       </c>
       <c r="F3" t="n">
-        <v>1.644</v>
+        <v>1.8906</v>
       </c>
       <c r="G3" t="n">
         <v>0.9157999999999999</v>
@@ -688,13 +688,13 @@
         <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>0.728</v>
+        <v>0.7078</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0106</v>
+        <v>0.7439</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2826</v>
+        <v>-0.0361</v>
       </c>
       <c r="V3" t="n">
         <v>0.1952</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3585</v>
+        <v>1.5505</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5281</v>
+        <v>0.641</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1696</v>
+        <v>0.9094</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7517</v>
+        <v>0.187</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3747</v>
+        <v>-1.7789</v>
       </c>
       <c r="I4" t="n">
-        <v>1.377</v>
+        <v>1.9659</v>
       </c>
       <c r="J4" t="n">
-        <v>1.331</v>
+        <v>0.8461</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0616</v>
+        <v>-1.6266</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2694</v>
+        <v>2.4727</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4207</v>
+        <v>-0.6592</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3131</v>
+        <v>-0.1523</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1076</v>
+        <v>-0.5068</v>
       </c>
       <c r="P4" t="n">
-        <v>1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1267</v>
+        <v>0.8415</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1971</v>
+        <v>0.84</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0704</v>
+        <v>0.0015</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.8249</v>
+        <v>0.7395</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.8249</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7074</v>
+        <v>1.3538</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0138</v>
+        <v>1.7083</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6937</v>
+        <v>-0.3545</v>
       </c>
       <c r="G5" t="n">
-        <v>0.187</v>
+        <v>2.7517</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7789</v>
+        <v>1.3747</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9659</v>
+        <v>1.377</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8461</v>
+        <v>1.331</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.6266</v>
+        <v>1.0616</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4727</v>
+        <v>0.2694</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6592</v>
+        <v>1.4207</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1523</v>
+        <v>0.3131</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5068</v>
+        <v>1.1076</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0016</v>
+        <v>0.122</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2127</v>
+        <v>0.3773</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2143</v>
+        <v>-0.2554</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7395</v>
+        <v>-2.8249</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3904</v>
+        <v>-2.8249</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7869</v>
+        <v>0.2112</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5745</v>
+        <v>-0.7922</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7876</v>
+        <v>1.0034</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2513</v>
@@ -922,13 +922,13 @@
         <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4214</v>
+        <v>1.4195</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4867</v>
+        <v>1.269</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0653</v>
+        <v>0.1505</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1745</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9347</v>
+        <v>-0.7943</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4047</v>
+        <v>0.4765</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.53</v>
+        <v>-1.2708</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.0467</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3285</v>
+        <v>-1.6818</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1952</v>
+        <v>1.6351</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0747</v>
+        <v>-0.402</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0365</v>
+        <v>-1.7789</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0382</v>
+        <v>1.377</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5985</v>
+        <v>0.3553</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.365</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2335</v>
+        <v>0.2582</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4591</v>
+        <v>1.2927</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6081</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.149</v>
+        <v>0.4143</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-3.7804</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-3.7804</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2836</v>
+        <v>-1.1582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1412</v>
+        <v>-0.6282</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4249</v>
+        <v>-0.53</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0467</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6818</v>
+        <v>-0.3285</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6351</v>
+        <v>-0.1952</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.402</v>
+        <v>0.0747</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7789</v>
+        <v>0.0365</v>
       </c>
       <c r="L8" t="n">
-        <v>1.377</v>
+        <v>0.0382</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3553</v>
+        <v>-0.5985</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.365</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2582</v>
+        <v>-0.2335</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7401</v>
+        <v>-0.87</v>
       </c>
       <c r="Q8" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2175</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2355</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.149</v>
+      </c>
+      <c r="V8" t="n">
         <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.7401</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.8033</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.5432</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.2602</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-3.7804</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.7804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9538</v>
+        <v>-2.055</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7608</v>
+        <v>-1.7966</v>
       </c>
       <c r="F9" t="n">
-        <v>1.807</v>
+        <v>-0.2584</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6402</v>
+        <v>1.6335</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1469</v>
+        <v>1.3171</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4933</v>
+        <v>0.3163</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.2673</v>
+        <v>0.4127</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.5605</v>
+        <v>0.3745</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7068</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6271</v>
+        <v>1.2207</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4136</v>
+        <v>0.9426</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2136</v>
+        <v>0.2781</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R9" t="n">
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.644</v>
+        <v>-0.9484</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5516</v>
+        <v>-0.6417</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0924</v>
+        <v>-0.3067</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0195</v>
+        <v>-2.2081</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9769</v>
+        <v>-3.9843</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0427</v>
+        <v>1.7762</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6335</v>
+        <v>-2.6402</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3171</v>
+        <v>-2.1469</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3163</v>
+        <v>-0.4933</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4127</v>
+        <v>-3.2673</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3745</v>
+        <v>-2.5605</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0382</v>
+        <v>-0.7068</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2207</v>
+        <v>0.6271</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9426</v>
+        <v>0.4136</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2781</v>
+        <v>0.2136</v>
       </c>
       <c r="P10" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-2.1751</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-3.2626</v>
       </c>
       <c r="R10" t="n">
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9129</v>
+        <v>0.3897</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.822</v>
+        <v>0.3281</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.091</v>
+        <v>0.0616</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7812</v>
+        <v>-3.3967</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.833</v>
+        <v>-2.5409</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9482</v>
+        <v>-0.8557</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1408</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1629</v>
+        <v>-0.7784</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.548</v>
+        <v>-0.256</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6149</v>
+        <v>-0.5224</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.253</v>
+        <v>-5.3552</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8976</v>
+        <v>-4.3388</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3554</v>
+        <v>-1.0163</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2684</v>
@@ -1390,13 +1390,13 @@
         <v>2.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5719</v>
+        <v>0.326</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0529</v>
+        <v>0.5059</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.519</v>
+        <v>-0.18</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3252</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.664199999999998</v>
+        <v>-6.321700000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.457800000000001</v>
+        <v>-7.1151</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7933000000000003</v>
+        <v>0.7935000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-3.298400000000001</v>
@@ -1441,7 +1441,7 @@
         <v>-2.2352</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.883400000000001</v>
+        <v>-3.8834</v>
       </c>
       <c r="K13" t="n">
         <v>-2.3694</v>
@@ -1468,13 +1468,13 @@
         <v>15.2255</v>
       </c>
       <c r="S13" t="n">
-        <v>6.825599999999997</v>
+        <v>7.1682</v>
       </c>
       <c r="T13" t="n">
-        <v>6.7416</v>
+        <v>7.084099999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08410000000000017</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-11.2791</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1259</v>
+        <v>5.3205</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5495</v>
+        <v>2.9907</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5763</v>
+        <v>2.3298</v>
       </c>
       <c r="G14" t="n">
         <v>2.0529</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1611</v>
+        <v>0.3557</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0347</v>
+        <v>0.4759</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1264</v>
+        <v>-0.1202</v>
       </c>
       <c r="V14" t="n">
         <v>3.5645</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.582</v>
+        <v>2.9283</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4653</v>
+        <v>2.1301</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1167</v>
+        <v>0.7983</v>
       </c>
       <c r="G15" t="n">
         <v>1.0572</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2572</v>
+        <v>-0.9109</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2211</v>
+        <v>-0.1142</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4783</v>
+        <v>-0.7967</v>
       </c>
       <c r="V15" t="n">
         <v>2.9995</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3619</v>
+        <v>1.9452</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2476</v>
+        <v>0.0517</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6096</v>
+        <v>1.8935</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7445</v>
+        <v>3.4005</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0346</v>
+        <v>2.6155</v>
       </c>
       <c r="I16" t="n">
-        <v>0.29</v>
+        <v>0.7849</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.5747</v>
+        <v>2.0205</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6512</v>
+        <v>1.9408</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0765</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1698</v>
+        <v>1.38</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3834</v>
+        <v>0.6748</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2136</v>
+        <v>0.7052</v>
       </c>
       <c r="P16" t="n">
-        <v>1.305</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R16" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6714</v>
+        <v>-0.5194</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1971</v>
+        <v>0.1214</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4743</v>
+        <v>-0.6408</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>1.6743</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ALDERETE DIAZ</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6598</v>
+        <v>1.8264</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3403</v>
+        <v>-0.1359</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3195</v>
+        <v>1.9623</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9115</v>
+        <v>-1.7445</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2717</v>
+        <v>-2.0346</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3602</v>
+        <v>0.29</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3451</v>
+        <v>-1.5747</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4964</v>
+        <v>-1.6512</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1514</v>
+        <v>0.0765</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5664</v>
+        <v>-0.1698</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7752</v>
+        <v>-0.3834</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2088</v>
+        <v>0.2136</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.305</v>
+        <v>1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2486</v>
+        <v>1.1359</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3878</v>
+        <v>0.3088</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1392</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2085</v>
+        <v>1.4886</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8605</v>
+        <v>-0.637</v>
       </c>
       <c r="F18" t="n">
-        <v>2.069</v>
+        <v>2.1256</v>
       </c>
       <c r="G18" t="n">
         <v>1.397</v>
@@ -1858,13 +1858,13 @@
         <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8187</v>
+        <v>-0.5387</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8904</v>
+        <v>-0.6669</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0717</v>
+        <v>0.1283</v>
       </c>
       <c r="V18" t="n">
         <v>0.1952</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2176</v>
+        <v>1.001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7306</v>
+        <v>0.9922</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9482</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4005</v>
+        <v>-1.9456</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6155</v>
+        <v>-1.1042</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7849</v>
+        <v>-0.8415</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0205</v>
+        <v>-1.653</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9408</v>
+        <v>-0.8514</v>
       </c>
       <c r="L19" t="n">
-        <v>0.07969999999999999</v>
+        <v>-0.8016</v>
       </c>
       <c r="M19" t="n">
-        <v>1.38</v>
+        <v>-0.2926</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6748</v>
+        <v>-0.2528</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7052</v>
+        <v>-0.0399</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.6101</v>
+        <v>1.7401</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.2471</v>
+        <v>-1.2486</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6609</v>
+        <v>-0.3749</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.5861</v>
+        <v>-0.8736</v>
       </c>
       <c r="V19" t="n">
-        <v>1.6743</v>
+        <v>2.4552</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2599</v>
+        <v>3.0202</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5857</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>D. ALDERETE DIAZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1139</v>
+        <v>0.3559</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5452</v>
+        <v>-0.1126</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6591</v>
+        <v>0.4685</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9456</v>
+        <v>1.9115</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1042</v>
+        <v>2.2717</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8415</v>
+        <v>-0.3602</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.653</v>
+        <v>1.3451</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8514</v>
+        <v>1.4964</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8016</v>
+        <v>-0.1514</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2926</v>
+        <v>0.5664</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2528</v>
+        <v>0.7752</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0399</v>
+        <v>-0.2088</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7401</v>
+        <v>-1.305</v>
       </c>
       <c r="Q20" t="n">
+        <v>-2.3926</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.0875</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.0553</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.9349</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.9902</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.1952</v>
+      </c>
+      <c r="W20" t="n">
         <v>0</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.7401</v>
-      </c>
-      <c r="S20" t="n">
-        <v>-2.3635</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-0.822</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-1.5415</v>
-      </c>
-      <c r="V20" t="n">
-        <v>2.4552</v>
-      </c>
-      <c r="W20" t="n">
-        <v>3.0202</v>
-      </c>
       <c r="X20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. TABOADA HEISKANEN</t>
+          <t>M. LAPORNIK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1109</v>
+        <v>-0.8147</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.168</v>
+        <v>-1.1538</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0571</v>
+        <v>0.3391</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1051</v>
+        <v>0.0303</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2312</v>
+        <v>-1.8097</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3363</v>
+        <v>1.84</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0565</v>
+        <v>-0.9648</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0182</v>
+        <v>-2.2685</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0382</v>
+        <v>1.3037</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0486</v>
+        <v>0.995</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2495</v>
+        <v>0.4588</v>
       </c>
       <c r="O21" t="n">
-        <v>0.298</v>
+        <v>0.5362</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R21" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5635</v>
+        <v>-2.3007</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.137</v>
+        <v>-0.5996</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4265</v>
+        <v>-1.701</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.5857</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.7156</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. LAPORNIK</t>
+          <t>C. TABOADA HEISKANEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8795</v>
+        <v>-1.0801</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4891</v>
+        <v>-1.168</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3904</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0303</v>
+        <v>0.1051</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8097</v>
+        <v>-0.2312</v>
       </c>
       <c r="I22" t="n">
-        <v>1.84</v>
+        <v>0.3363</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9648</v>
+        <v>0.0565</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.2685</v>
+        <v>0.0182</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3037</v>
+        <v>0.0382</v>
       </c>
       <c r="M22" t="n">
-        <v>0.995</v>
+        <v>0.0486</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4588</v>
+        <v>-0.2495</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5362</v>
+        <v>0.298</v>
       </c>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1751</v>
+        <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.3655</v>
+        <v>-0.5327</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9349</v>
+        <v>-0.137</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.4306</v>
+        <v>-0.3957</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5857</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7156</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3871</v>
+        <v>-4.8167</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6329</v>
+        <v>-3.1859</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7541</v>
+        <v>-1.6308</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9657</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2913</v>
+        <v>-0.721</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4795</v>
+        <v>-0.0324</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8119</v>
+        <v>-0.6886</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.664299999999997</v>
+        <v>8.154399999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2283999999999997</v>
+        <v>-0.2285000000000004</v>
       </c>
       <c r="F24" t="n">
-        <v>6.8928</v>
+        <v>8.382999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>3.2987</v>
@@ -2296,16 +2296,16 @@
         <v>1.0632</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2351</v>
+        <v>2.235099999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5847999999999993</v>
+        <v>-0.5847999999999998</v>
       </c>
       <c r="K24" t="n">
         <v>-1.3063</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7212000000000005</v>
+        <v>0.7212000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>3.8833</v>
@@ -2326,13 +2326,13 @@
         <v>14.1379</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.8257</v>
+        <v>-5.3357</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.08399999999999991</v>
+        <v>-0.08400000000000009</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.7417</v>
+        <v>-5.2514</v>
       </c>
       <c r="V24" t="n">
         <v>11.2792</v>
